--- a/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59278649923302</v>
+        <v>44.86538503290939</v>
       </c>
       <c r="M2" t="n">
-        <v>99.70892812048268</v>
+        <v>101.8483628927591</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99174468925681</v>
+        <v>88.066229887578</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93900096905959</v>
+        <v>45.92746522900391</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228631523799038</v>
+        <v>2.228831341116531</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710187096140172</v>
+        <v>5.70785200260734</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428771745996792</v>
+        <v>0.7429437803721771</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97709826024475</v>
+        <v>33.97227867608881</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17235003158524</v>
+        <v>34.17541389712014</v>
       </c>
       <c r="I3" t="n">
-        <v>6.517618261639928</v>
+        <v>6.595511562946895</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642982341247995</v>
+        <v>4.643398627326107</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00825531074319</v>
+        <v>11.93377011242199</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81878424535214</v>
+        <v>48.90203031474912</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7660405251549</v>
+        <v>106.763265656175</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.98006027446033</v>
+        <v>87.08542853110779</v>
       </c>
       <c r="C4" t="n">
-        <v>42.55233439854824</v>
+        <v>42.58714771634616</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179377448082665</v>
+        <v>2.181258576451814</v>
       </c>
       <c r="E4" t="n">
-        <v>6.491101453509242</v>
+        <v>6.503996592072306</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444266640921974</v>
+        <v>0.7445100663725116</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22618427896894</v>
+        <v>33.24716538969175</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24362654824107</v>
+        <v>34.24746305313553</v>
       </c>
       <c r="I4" t="n">
-        <v>5.442677230989966</v>
+        <v>5.507846938555685</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652666650576234</v>
+        <v>4.653187914828198</v>
       </c>
       <c r="K4" t="n">
-        <v>13.01993972553969</v>
+        <v>12.9145714688922</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24668092419984</v>
+        <v>44.31507216023533</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81895504828776</v>
+        <v>99.81679134547369</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.74916695886091</v>
+        <v>86.00202640019084</v>
       </c>
       <c r="C5" t="n">
-        <v>42.1661239222467</v>
+        <v>42.35850723513752</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119085119648133</v>
+        <v>2.128688592359804</v>
       </c>
       <c r="E5" t="n">
-        <v>7.068788107265958</v>
+        <v>7.113587394563347</v>
       </c>
       <c r="F5" t="n">
-        <v>0.74574149067544</v>
+        <v>0.7458368941054694</v>
       </c>
       <c r="G5" t="n">
-        <v>32.30698415742217</v>
+        <v>32.44588351760686</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30410857107024</v>
+        <v>34.30849712885159</v>
       </c>
       <c r="I5" t="n">
-        <v>4.543575196057468</v>
+        <v>4.598052284544595</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660884316721501</v>
+        <v>4.661480588159185</v>
       </c>
       <c r="K5" t="n">
-        <v>14.25083304113909</v>
+        <v>13.99797359980913</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43185755797562</v>
+        <v>43.49052341676014</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8488145213614</v>
+        <v>99.84700425170679</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.29058371597952</v>
+        <v>84.62894974406262</v>
       </c>
       <c r="C6" t="n">
-        <v>41.41306774269386</v>
+        <v>41.69953811536064</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047663303754672</v>
+        <v>2.061687835318489</v>
       </c>
       <c r="E6" t="n">
-        <v>7.462539520185123</v>
+        <v>7.529269928667595</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468597827109131</v>
+        <v>0.7469642272008166</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2181069560441</v>
+        <v>31.42464501125302</v>
       </c>
       <c r="H6" t="n">
-        <v>34.355550004702</v>
+        <v>34.36035445123756</v>
       </c>
       <c r="I6" t="n">
-        <v>3.791990506639528</v>
+        <v>3.837501870380027</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667873641943207</v>
+        <v>4.668526420005104</v>
       </c>
       <c r="K6" t="n">
-        <v>15.70941628402046</v>
+        <v>15.37105025593739</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75130555117296</v>
+        <v>42.80168795413127</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87378957788728</v>
+        <v>99.8722763254293</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.65262661550361</v>
+        <v>83.14880281964443</v>
       </c>
       <c r="C7" t="n">
-        <v>40.36387781036324</v>
+        <v>40.81540644890784</v>
       </c>
       <c r="D7" t="n">
-        <v>1.967820903393245</v>
+        <v>1.989837842860863</v>
       </c>
       <c r="E7" t="n">
-        <v>7.698897887431379</v>
+        <v>7.800544785498443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478128004310105</v>
+        <v>0.7479230691535861</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00085185871441</v>
+        <v>30.32949352014802</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39938881982648</v>
+        <v>34.40446118106496</v>
       </c>
       <c r="I7" t="n">
-        <v>3.164024343013264</v>
+        <v>3.202023238708629</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673830002693816</v>
+        <v>4.674519182209914</v>
       </c>
       <c r="K7" t="n">
-        <v>17.34737338449641</v>
+        <v>16.85119718035559</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18341573551148</v>
+        <v>42.22679909655936</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89466693037113</v>
+        <v>99.89340272582278</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.75400546007246</v>
+        <v>87.97962882885473</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73513022039955</v>
+        <v>43.11340884683535</v>
       </c>
       <c r="D8" t="n">
-        <v>1.972131198148366</v>
+        <v>1.994069084673628</v>
       </c>
       <c r="E8" t="n">
-        <v>9.586005879365663</v>
+        <v>9.629192097868845</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749450801931021</v>
+        <v>0.7495134717958355</v>
       </c>
       <c r="G8" t="n">
-        <v>30.52114893255579</v>
+        <v>30.8323116419224</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47473688882696</v>
+        <v>34.47761970260843</v>
       </c>
       <c r="I8" t="n">
-        <v>5.766464247175785</v>
+        <v>5.612463631261631</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684067512068881</v>
+        <v>4.684459198723973</v>
       </c>
       <c r="K8" t="n">
-        <v>12.24599453992754</v>
+        <v>12.02037117114526</v>
       </c>
       <c r="L8" t="n">
-        <v>44.82707987137766</v>
+        <v>44.67953483302764</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80820463170475</v>
+        <v>99.81331485100824</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.71806851318335</v>
+        <v>85.90804614108649</v>
       </c>
       <c r="C9" t="n">
-        <v>41.59369767721949</v>
+        <v>41.91301244616768</v>
       </c>
       <c r="D9" t="n">
-        <v>1.880226418121015</v>
+        <v>1.900218645864519</v>
       </c>
       <c r="E9" t="n">
-        <v>9.941678392184913</v>
+        <v>9.956922237235405</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508539069279064</v>
+        <v>0.7508761254752033</v>
       </c>
       <c r="G9" t="n">
-        <v>29.09880974870118</v>
+        <v>29.38119542968385</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53927971868369</v>
+        <v>34.54030177185935</v>
       </c>
       <c r="I9" t="n">
-        <v>4.814383410265242</v>
+        <v>4.685556146748146</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692836918299416</v>
+        <v>4.692975784220022</v>
       </c>
       <c r="K9" t="n">
-        <v>14.28193148681664</v>
+        <v>14.09195385891351</v>
       </c>
       <c r="L9" t="n">
-        <v>43.96419127354233</v>
+        <v>43.83913192738376</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83982043757845</v>
+        <v>99.84409823246494</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.57215542650523</v>
+        <v>83.73816858791717</v>
       </c>
       <c r="C10" t="n">
-        <v>40.1943197417937</v>
+        <v>40.47010657213801</v>
       </c>
       <c r="D10" t="n">
-        <v>1.784481471254384</v>
+        <v>1.803035457900248</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10516402253428</v>
+        <v>10.09947851800591</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520573554919282</v>
+        <v>0.7520450299811176</v>
       </c>
       <c r="G10" t="n">
-        <v>27.61703927339011</v>
+        <v>27.87854822417825</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5946383526287</v>
+        <v>34.59407137913141</v>
       </c>
       <c r="I10" t="n">
-        <v>4.018416479381266</v>
+        <v>3.91070854133825</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700358471824552</v>
+        <v>4.700281437381985</v>
       </c>
       <c r="K10" t="n">
-        <v>16.42784457349479</v>
+        <v>16.26183141208283</v>
       </c>
       <c r="L10" t="n">
-        <v>43.24410281220414</v>
+        <v>43.1379076783695</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86626712749263</v>
+        <v>99.86984566259034</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.27719701394803</v>
+        <v>81.47827311773428</v>
       </c>
       <c r="C11" t="n">
-        <v>38.52189711002759</v>
+        <v>38.8163657239574</v>
       </c>
       <c r="D11" t="n">
-        <v>1.683131803132897</v>
+        <v>1.702878395661256</v>
       </c>
       <c r="E11" t="n">
-        <v>10.0901219320601</v>
+        <v>10.08234030028331</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530916198116184</v>
+        <v>0.7530490315412224</v>
       </c>
       <c r="G11" t="n">
-        <v>26.04852886297456</v>
+        <v>26.3299189515884</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64221451133445</v>
+        <v>34.64025545089623</v>
       </c>
       <c r="I11" t="n">
-        <v>3.353285660811787</v>
+        <v>3.263274540631228</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706822623822616</v>
+        <v>4.70655644713264</v>
       </c>
       <c r="K11" t="n">
-        <v>18.72280298605197</v>
+        <v>18.52172688226571</v>
       </c>
       <c r="L11" t="n">
-        <v>42.64367722393764</v>
+        <v>42.55327660096194</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8883773200172</v>
+        <v>99.89136920718505</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.89862334217669</v>
+        <v>78.97949578674765</v>
       </c>
       <c r="C12" t="n">
-        <v>36.66203466576502</v>
+        <v>36.82264192317523</v>
       </c>
       <c r="D12" t="n">
-        <v>1.579145667136599</v>
+        <v>1.593068370564424</v>
       </c>
       <c r="E12" t="n">
-        <v>9.933025301412981</v>
+        <v>9.885934466368829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539817621671884</v>
+        <v>0.7539143156843771</v>
       </c>
       <c r="G12" t="n">
-        <v>24.43921587880603</v>
+        <v>24.63203549247697</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68316105969067</v>
+        <v>34.68005852148134</v>
       </c>
       <c r="I12" t="n">
-        <v>2.797707659418297</v>
+        <v>2.722520147144371</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712386013544927</v>
+        <v>4.711964473027357</v>
       </c>
       <c r="K12" t="n">
-        <v>21.10137665782331</v>
+        <v>21.02050421325233</v>
       </c>
       <c r="L12" t="n">
-        <v>42.14344185250022</v>
+        <v>42.06620734855489</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90685317608855</v>
+        <v>99.90935348498246</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.39542805714201</v>
+        <v>76.60430962314622</v>
       </c>
       <c r="C13" t="n">
-        <v>34.59074383274069</v>
+        <v>34.86789427970765</v>
       </c>
       <c r="D13" t="n">
-        <v>1.470690213198105</v>
+        <v>1.489755786964706</v>
       </c>
       <c r="E13" t="n">
-        <v>9.639793013516067</v>
+        <v>9.623320049594694</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547495395581864</v>
+        <v>0.7546593329644221</v>
       </c>
       <c r="G13" t="n">
-        <v>22.76073471826627</v>
+        <v>23.03461552415122</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71847881967658</v>
+        <v>34.71432931636341</v>
       </c>
       <c r="I13" t="n">
-        <v>2.333797130688145</v>
+        <v>2.271008782080118</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717184622238665</v>
+        <v>4.716620831027639</v>
       </c>
       <c r="K13" t="n">
-        <v>23.60457194285797</v>
+        <v>23.39569037685377</v>
       </c>
       <c r="L13" t="n">
-        <v>41.72697012275084</v>
+        <v>41.66078978379568</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9222858983495</v>
+        <v>99.92437444035711</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.21205535251731</v>
+        <v>83.43194720331449</v>
       </c>
       <c r="C14" t="n">
-        <v>38.90746503475574</v>
+        <v>39.20931950033744</v>
       </c>
       <c r="D14" t="n">
-        <v>1.472384015439324</v>
+        <v>1.491410514713155</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0336989928914</v>
+        <v>12.02156289163642</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556187888740454</v>
+        <v>0.7554975614511372</v>
       </c>
       <c r="G14" t="n">
-        <v>24.69057318520999</v>
+        <v>24.98439979747742</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66208908817112</v>
+        <v>36.67708668680729</v>
       </c>
       <c r="I14" t="n">
-        <v>2.87507385146864</v>
+        <v>2.780129992159469</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722617430462784</v>
+        <v>4.721859759069608</v>
       </c>
       <c r="K14" t="n">
-        <v>16.78794464748271</v>
+        <v>16.56805279668551</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20886477036724</v>
+        <v>44.13005952219616</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90427445260568</v>
+        <v>99.90743181921911</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.42836543012524</v>
+        <v>82.64452663964627</v>
       </c>
       <c r="C15" t="n">
-        <v>38.55765469918669</v>
+        <v>38.85157936718764</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44238736862782</v>
+        <v>1.462271782502645</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19849753277907</v>
+        <v>12.17317950945423</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563516025196249</v>
+        <v>0.7562041841459558</v>
       </c>
       <c r="G15" t="n">
-        <v>24.19781215094411</v>
+        <v>24.49626207284897</v>
       </c>
       <c r="H15" t="n">
-        <v>36.707900798316</v>
+        <v>36.71139104880012</v>
       </c>
       <c r="I15" t="n">
-        <v>2.398218461190946</v>
+        <v>2.318941890982117</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727197515747656</v>
+        <v>4.726276150912224</v>
       </c>
       <c r="K15" t="n">
-        <v>17.57163456987477</v>
+        <v>17.35547336035371</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79084756839776</v>
+        <v>43.71572143934312</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92013683745922</v>
+        <v>99.92277416688448</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.8662689939212</v>
+        <v>80.18977449742461</v>
       </c>
       <c r="C16" t="n">
-        <v>36.36603811605423</v>
+        <v>36.75524066936654</v>
       </c>
       <c r="D16" t="n">
-        <v>1.345844442555419</v>
+        <v>1.369237035202733</v>
       </c>
       <c r="E16" t="n">
-        <v>11.71538273531073</v>
+        <v>11.72101425561309</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569830089143585</v>
+        <v>0.7568121181705965</v>
       </c>
       <c r="G16" t="n">
-        <v>22.5781864939163</v>
+        <v>22.93772584243669</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73854475176847</v>
+        <v>36.74090437890112</v>
       </c>
       <c r="I16" t="n">
-        <v>2.00018375574119</v>
+        <v>1.93400512853414</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731143805714741</v>
+        <v>4.730075738566228</v>
       </c>
       <c r="K16" t="n">
-        <v>20.1337310060788</v>
+        <v>19.81022550257539</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43361369838944</v>
+        <v>43.37011877553078</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93338282052248</v>
+        <v>99.93558494747272</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.64383120470751</v>
+        <v>81.80095010729517</v>
       </c>
       <c r="C17" t="n">
-        <v>37.66679736002252</v>
+        <v>37.94798103666354</v>
       </c>
       <c r="D17" t="n">
-        <v>1.346928159007324</v>
+        <v>1.370295260838136</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52488363329541</v>
+        <v>12.47016959013582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575925555414675</v>
+        <v>0.7573970263815498</v>
       </c>
       <c r="G17" t="n">
-        <v>23.06772350706978</v>
+        <v>23.37944755556985</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2394841326278</v>
+        <v>37.19329398736707</v>
       </c>
       <c r="I17" t="n">
-        <v>1.972265745031553</v>
+        <v>1.896615272118059</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734953472134173</v>
+        <v>4.733731414884687</v>
       </c>
       <c r="K17" t="n">
-        <v>18.35616879529248</v>
+        <v>18.19904989270482</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91134454828012</v>
+        <v>43.78979738429675</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93431070359512</v>
+        <v>99.93682831366512</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.02660963491005</v>
+        <v>79.47127262259454</v>
       </c>
       <c r="C18" t="n">
-        <v>35.35383208303755</v>
+        <v>35.91105073601889</v>
       </c>
       <c r="D18" t="n">
-        <v>1.252364476545421</v>
+        <v>1.285377531736704</v>
       </c>
       <c r="E18" t="n">
-        <v>11.91966591254045</v>
+        <v>11.96098187259554</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581181205683731</v>
+        <v>0.7578994593998635</v>
       </c>
       <c r="G18" t="n">
-        <v>21.44820960333704</v>
+        <v>21.93061411740215</v>
       </c>
       <c r="H18" t="n">
-        <v>37.2653182968325</v>
+        <v>37.21796683173824</v>
       </c>
       <c r="I18" t="n">
-        <v>1.644694971533924</v>
+        <v>1.581561188472888</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738238253552333</v>
+        <v>4.736871621249147</v>
       </c>
       <c r="K18" t="n">
-        <v>20.97339036508997</v>
+        <v>20.52872737740546</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61799239228827</v>
+        <v>43.50753812901681</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94521484041577</v>
+        <v>99.94731624244116</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.93721329489256</v>
+        <v>78.53191678421709</v>
       </c>
       <c r="C19" t="n">
-        <v>34.51051857807849</v>
+        <v>35.2129296712755</v>
       </c>
       <c r="D19" t="n">
-        <v>1.213382272581076</v>
+        <v>1.251659112857954</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77831755227584</v>
+        <v>11.86736505152303</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758564941249082</v>
+        <v>0.7583243810197925</v>
       </c>
       <c r="G19" t="n">
-        <v>20.7805936679716</v>
+        <v>21.35532350058259</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28728178040647</v>
+        <v>37.23883334451967</v>
       </c>
       <c r="I19" t="n">
-        <v>1.378042197601735</v>
+        <v>1.320884012340345</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741030882806763</v>
+        <v>4.739527381373704</v>
       </c>
       <c r="K19" t="n">
-        <v>22.06278670510744</v>
+        <v>21.4680832157829</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38078703402604</v>
+        <v>43.27498231745921</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95409231721197</v>
+        <v>99.95599520451761</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.18169292599782</v>
+        <v>75.94708307118272</v>
       </c>
       <c r="C20" t="n">
-        <v>31.96673281484976</v>
+        <v>32.83129444577403</v>
       </c>
       <c r="D20" t="n">
-        <v>1.114948692769859</v>
+        <v>1.158371259558684</v>
       </c>
       <c r="E20" t="n">
-        <v>11.01431375710895</v>
+        <v>11.16641900581157</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758951363263612</v>
+        <v>0.7586909164566793</v>
       </c>
       <c r="G20" t="n">
-        <v>19.09480323608274</v>
+        <v>19.76368224186004</v>
       </c>
       <c r="H20" t="n">
-        <v>37.30627636578529</v>
+        <v>37.2568327025658</v>
       </c>
       <c r="I20" t="n">
-        <v>1.148953490589806</v>
+        <v>1.101268717075703</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743446020397576</v>
+        <v>4.741818227854247</v>
       </c>
       <c r="K20" t="n">
-        <v>24.81830707400218</v>
+        <v>24.05291692881728</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17668116121467</v>
+        <v>43.07909740284366</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96172105006661</v>
+        <v>99.96330877743497</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.30390106211205</v>
+        <v>81.7084891085092</v>
       </c>
       <c r="C21" t="n">
-        <v>35.84646812060747</v>
+        <v>36.47534829640151</v>
       </c>
       <c r="D21" t="n">
-        <v>1.115659345310869</v>
+        <v>1.15907824520605</v>
       </c>
       <c r="E21" t="n">
-        <v>13.0838458093021</v>
+        <v>13.11310611480668</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594351081375278</v>
+        <v>0.7591539662641532</v>
       </c>
       <c r="G21" t="n">
-        <v>20.91037589007706</v>
+        <v>21.46627187235627</v>
       </c>
       <c r="H21" t="n">
-        <v>39.13345675539927</v>
+        <v>38.97009888101751</v>
       </c>
       <c r="I21" t="n">
-        <v>1.554658728025665</v>
+        <v>1.496067739707589</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746469425859549</v>
+        <v>4.744712289150959</v>
       </c>
       <c r="K21" t="n">
-        <v>18.69609893788794</v>
+        <v>18.29151089149079</v>
       </c>
       <c r="L21" t="n">
-        <v>45.40564399344738</v>
+        <v>45.183302305254</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94821105194279</v>
+        <v>99.9501614931463</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.86538503290939</v>
+        <v>45.43034227803824</v>
       </c>
       <c r="M2" t="n">
-        <v>101.8483628927591</v>
+        <v>99.21299653448472</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.066229887578</v>
+        <v>88.09953076970606</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92746522900391</v>
+        <v>45.95725561314313</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228831341116531</v>
+        <v>2.228894089334946</v>
       </c>
       <c r="E3" t="n">
-        <v>5.70785200260734</v>
+        <v>5.726632312658838</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429437803721771</v>
+        <v>0.7429646964449821</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97227867608881</v>
+        <v>33.9822819841404</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17541389712014</v>
+        <v>34.17637603646917</v>
       </c>
       <c r="I3" t="n">
-        <v>6.595511562946895</v>
+        <v>6.598852297876592</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643398627326107</v>
+        <v>4.643529352781138</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93377011242199</v>
+        <v>11.90046923029394</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90203031474912</v>
+        <v>48.90542757086736</v>
       </c>
       <c r="M3" t="n">
-        <v>106.763265656175</v>
+        <v>106.7631524143044</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08542853110779</v>
+        <v>87.28937965311414</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58714771634616</v>
+        <v>42.7871292295812</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181258576451814</v>
+        <v>2.190436256955797</v>
       </c>
       <c r="E4" t="n">
-        <v>6.503996592072306</v>
+        <v>6.546259643436955</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445100663725116</v>
+        <v>0.7445281523023775</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24716538969175</v>
+        <v>33.39594416276952</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24746305313553</v>
+        <v>34.24829500590936</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507846938555685</v>
+        <v>5.510615479850255</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653187914828198</v>
+        <v>4.653300951889859</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9145714688922</v>
+        <v>12.71062034688588</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31507216023533</v>
+        <v>44.31894897081413</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81679134547369</v>
+        <v>99.81669854728121</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.00202640019084</v>
+        <v>86.25281929759304</v>
       </c>
       <c r="C5" t="n">
-        <v>42.35850723513752</v>
+        <v>42.60597112103388</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128688592359804</v>
+        <v>2.140344925308375</v>
       </c>
       <c r="E5" t="n">
-        <v>7.113587394563347</v>
+        <v>7.163282441017729</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458368941054694</v>
+        <v>0.7458518135599805</v>
       </c>
       <c r="G5" t="n">
-        <v>32.44588351760686</v>
+        <v>32.63223907460551</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30849712885159</v>
+        <v>34.30918342375911</v>
       </c>
       <c r="I5" t="n">
-        <v>4.598052284544595</v>
+        <v>4.600343784592454</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661480588159185</v>
+        <v>4.661573834749879</v>
       </c>
       <c r="K5" t="n">
-        <v>13.99797359980913</v>
+        <v>13.74718070240696</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49052341676014</v>
+        <v>43.4937755243411</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84700425170679</v>
+        <v>99.84692734778194</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.62894974406262</v>
+        <v>84.94715041032558</v>
       </c>
       <c r="C6" t="n">
-        <v>41.69953811536064</v>
+        <v>42.01498600397309</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061687835318489</v>
+        <v>2.076829713688088</v>
       </c>
       <c r="E6" t="n">
-        <v>7.529269928667595</v>
+        <v>7.590609688834685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469642272008166</v>
+        <v>0.7469755004917085</v>
       </c>
       <c r="G6" t="n">
-        <v>31.42464501125302</v>
+        <v>31.66387012343341</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36035445123756</v>
+        <v>34.36087302261859</v>
       </c>
       <c r="I6" t="n">
-        <v>3.837501870380027</v>
+        <v>3.83939548318593</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668526420005104</v>
+        <v>4.668596878073178</v>
       </c>
       <c r="K6" t="n">
-        <v>15.37105025593739</v>
+        <v>15.05284958967441</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80168795413127</v>
+        <v>42.8043770790027</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8722763254293</v>
+        <v>99.87221267265021</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.14880281964443</v>
+        <v>83.40086409621135</v>
       </c>
       <c r="C7" t="n">
-        <v>40.81540644890784</v>
+        <v>41.06524808499835</v>
       </c>
       <c r="D7" t="n">
-        <v>1.989837842860863</v>
+        <v>2.001691079429898</v>
       </c>
       <c r="E7" t="n">
-        <v>7.800544785498443</v>
+        <v>7.84991746689296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479230691535861</v>
+        <v>0.7479319275875282</v>
       </c>
       <c r="G7" t="n">
-        <v>30.32949352014802</v>
+        <v>30.51828753631871</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40446118106496</v>
+        <v>34.4048686690263</v>
       </c>
       <c r="I7" t="n">
-        <v>3.202023238708629</v>
+        <v>3.203592869533897</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674519182209914</v>
+        <v>4.674574547422051</v>
       </c>
       <c r="K7" t="n">
-        <v>16.85119718035559</v>
+        <v>16.59913590378865</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22679909655936</v>
+        <v>42.22896613668004</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89340272582278</v>
+        <v>99.89335012546705</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.97962882885473</v>
+        <v>88.1386958538032</v>
       </c>
       <c r="C8" t="n">
-        <v>43.11340884683535</v>
+        <v>43.31535436374522</v>
       </c>
       <c r="D8" t="n">
-        <v>1.994069084673628</v>
+        <v>2.005907941769616</v>
       </c>
       <c r="E8" t="n">
-        <v>9.629192097868845</v>
+        <v>9.644020636348621</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495134717958355</v>
+        <v>0.7495075583182276</v>
       </c>
       <c r="G8" t="n">
-        <v>30.8323116419224</v>
+        <v>31.00716851484066</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47761970260843</v>
+        <v>34.47734768263847</v>
       </c>
       <c r="I8" t="n">
-        <v>5.612463631261631</v>
+        <v>5.57032128039867</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684459198723973</v>
+        <v>4.684422239488923</v>
       </c>
       <c r="K8" t="n">
-        <v>12.02037117114526</v>
+        <v>11.86130414619682</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67953483302764</v>
+        <v>44.63805444897378</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81331485100824</v>
+        <v>99.81471295891582</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.90804614108649</v>
+        <v>86.10673210262291</v>
       </c>
       <c r="C9" t="n">
-        <v>41.91301244616768</v>
+        <v>42.14829663348554</v>
       </c>
       <c r="D9" t="n">
-        <v>1.900218645864519</v>
+        <v>1.913795881649349</v>
       </c>
       <c r="E9" t="n">
-        <v>9.956922237235405</v>
+        <v>9.976211990682353</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508761254752033</v>
+        <v>0.750856824916473</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38119542968385</v>
+        <v>29.58330747370107</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54030177185935</v>
+        <v>34.53941394615777</v>
       </c>
       <c r="I9" t="n">
-        <v>4.685556146748146</v>
+        <v>4.650290829787944</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692975784220022</v>
+        <v>4.692855155727957</v>
       </c>
       <c r="K9" t="n">
-        <v>14.09195385891351</v>
+        <v>13.8932678973771</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83913192738376</v>
+        <v>43.80370432245962</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84409823246494</v>
+        <v>99.84526885332225</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.73816858791717</v>
+        <v>83.8488508305031</v>
       </c>
       <c r="C10" t="n">
-        <v>40.47010657213801</v>
+        <v>40.61216462518888</v>
       </c>
       <c r="D10" t="n">
-        <v>1.803035457900248</v>
+        <v>1.812397539061182</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09947851800591</v>
+        <v>10.09451421178836</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520450299811176</v>
+        <v>0.7520153547105383</v>
       </c>
       <c r="G10" t="n">
-        <v>27.87854822417825</v>
+        <v>28.01589980244816</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59407137913141</v>
+        <v>34.59270631668477</v>
       </c>
       <c r="I10" t="n">
-        <v>3.91070854133825</v>
+        <v>3.881221638869222</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700281437381985</v>
+        <v>4.700095966940864</v>
       </c>
       <c r="K10" t="n">
-        <v>16.26183141208283</v>
+        <v>16.1511491694969</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1379076783695</v>
+        <v>43.10751146004234</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86984566259034</v>
+        <v>99.87082525472812</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.47827311773428</v>
+        <v>81.49718285390571</v>
       </c>
       <c r="C11" t="n">
-        <v>38.8163657239574</v>
+        <v>38.86221749236492</v>
       </c>
       <c r="D11" t="n">
-        <v>1.702878395661256</v>
+        <v>1.707896949645133</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08234030028331</v>
+        <v>10.05224968924703</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530490315412224</v>
+        <v>0.7530115052133349</v>
       </c>
       <c r="G11" t="n">
-        <v>26.3299189515884</v>
+        <v>26.40053784168687</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64025545089623</v>
+        <v>34.63852923981342</v>
       </c>
       <c r="I11" t="n">
-        <v>3.263274540631228</v>
+        <v>3.238635720716581</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70655644713264</v>
+        <v>4.706321907583344</v>
       </c>
       <c r="K11" t="n">
-        <v>18.52172688226571</v>
+        <v>18.50281714609429</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55327660096194</v>
+        <v>42.52715364934998</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89136920718505</v>
+        <v>99.89218828780919</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.97949578674765</v>
+        <v>79.00414530050422</v>
       </c>
       <c r="C12" t="n">
-        <v>36.82264192317523</v>
+        <v>36.87046894915709</v>
       </c>
       <c r="D12" t="n">
-        <v>1.593068370564424</v>
+        <v>1.598139843821999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.885934466368829</v>
+        <v>9.856570411351411</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539143156843771</v>
+        <v>0.7538699377043477</v>
       </c>
       <c r="G12" t="n">
-        <v>24.63203549247697</v>
+        <v>24.70392106028227</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68005852148134</v>
+        <v>34.6780171344</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722520147144371</v>
+        <v>2.701939802292023</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711964473027357</v>
+        <v>4.711687110652173</v>
       </c>
       <c r="K12" t="n">
-        <v>21.02050421325233</v>
+        <v>20.99585469949577</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06620734855489</v>
+        <v>42.04371424799391</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90935348498246</v>
+        <v>99.91003789664677</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.60430962314622</v>
+        <v>76.56431919858856</v>
       </c>
       <c r="C13" t="n">
-        <v>34.86789427970765</v>
+        <v>34.84794456822937</v>
       </c>
       <c r="D13" t="n">
-        <v>1.489755786964706</v>
+        <v>1.491766703060341</v>
       </c>
       <c r="E13" t="n">
-        <v>9.623320049594694</v>
+        <v>9.576148852791112</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546593329644221</v>
+        <v>0.7546096606728954</v>
       </c>
       <c r="G13" t="n">
-        <v>23.03461552415122</v>
+        <v>23.05961334686855</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71432931636341</v>
+        <v>34.71204439095319</v>
       </c>
       <c r="I13" t="n">
-        <v>2.271008782080118</v>
+        <v>2.253825865036894</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716620831027639</v>
+        <v>4.716310379205596</v>
       </c>
       <c r="K13" t="n">
-        <v>23.39569037685377</v>
+        <v>23.43568080141143</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66078978379568</v>
+        <v>41.64132074696219</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92437444035711</v>
+        <v>99.924946116603</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.43194720331449</v>
+        <v>83.528001398698</v>
       </c>
       <c r="C14" t="n">
-        <v>39.20931950033744</v>
+        <v>39.12167736812759</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491410514713155</v>
+        <v>1.493559942576776</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02156289163642</v>
+        <v>11.96099848793033</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554975614511372</v>
+        <v>0.7555167702498996</v>
       </c>
       <c r="G14" t="n">
-        <v>24.98439979747742</v>
+        <v>24.95862998858541</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67708668680729</v>
+        <v>36.62506831662935</v>
       </c>
       <c r="I14" t="n">
-        <v>2.780129992159469</v>
+        <v>3.012248078664371</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721859759069608</v>
+        <v>4.721979814061872</v>
       </c>
       <c r="K14" t="n">
-        <v>16.56805279668551</v>
+        <v>16.471998601302</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13005952219616</v>
+        <v>44.30603631625306</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90743181921911</v>
+        <v>99.89971228568265</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.64452663964627</v>
+        <v>82.78675242956054</v>
       </c>
       <c r="C15" t="n">
-        <v>38.85157936718764</v>
+        <v>38.84582400890833</v>
       </c>
       <c r="D15" t="n">
-        <v>1.462271782502645</v>
+        <v>1.466221045015856</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17317950945423</v>
+        <v>12.16084921995061</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562041841459558</v>
+        <v>0.7562811526279429</v>
       </c>
       <c r="G15" t="n">
-        <v>24.49626207284897</v>
+        <v>24.501774251452</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71139104880012</v>
+        <v>36.66212316162849</v>
       </c>
       <c r="I15" t="n">
-        <v>2.318941890982117</v>
+        <v>2.512746394960979</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726276150912224</v>
+        <v>4.726757203924643</v>
       </c>
       <c r="K15" t="n">
-        <v>17.35547336035371</v>
+        <v>17.21324757043947</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71572143934312</v>
+        <v>43.85725486291153</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92277416688448</v>
+        <v>99.91632644225933</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.18977449742461</v>
+        <v>80.42107425654514</v>
       </c>
       <c r="C16" t="n">
-        <v>36.75524066936654</v>
+        <v>36.86844005088673</v>
       </c>
       <c r="D16" t="n">
-        <v>1.369237035202733</v>
+        <v>1.376444994278731</v>
       </c>
       <c r="E16" t="n">
-        <v>11.72101425561309</v>
+        <v>11.76554164139548</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568121181705965</v>
+        <v>0.7569381091957031</v>
       </c>
       <c r="G16" t="n">
-        <v>22.93772584243669</v>
+        <v>23.0015417075083</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74090437890112</v>
+        <v>36.69397034242279</v>
       </c>
       <c r="I16" t="n">
-        <v>1.93400512853414</v>
+        <v>2.095774279271001</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730075738566228</v>
+        <v>4.730863182473144</v>
       </c>
       <c r="K16" t="n">
-        <v>19.81022550257539</v>
+        <v>19.57892574345484</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37011877553078</v>
+        <v>43.48283569468728</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93558494747272</v>
+        <v>99.93020148902886</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.80095010729517</v>
+        <v>82.24208862072145</v>
       </c>
       <c r="C17" t="n">
-        <v>37.94798103666354</v>
+        <v>38.17230780660751</v>
       </c>
       <c r="D17" t="n">
-        <v>1.370295260838136</v>
+        <v>1.377625798686406</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47016959013582</v>
+        <v>12.58848268931065</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573970263815498</v>
+        <v>0.7575874601391772</v>
       </c>
       <c r="G17" t="n">
-        <v>23.37944755556985</v>
+        <v>23.48135855702916</v>
       </c>
       <c r="H17" t="n">
-        <v>37.19329398736707</v>
+        <v>37.18553345143901</v>
       </c>
       <c r="I17" t="n">
-        <v>1.896615272118059</v>
+        <v>2.116579038247193</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733731414884687</v>
+        <v>4.734921625869857</v>
       </c>
       <c r="K17" t="n">
-        <v>18.19904989270482</v>
+        <v>17.75791137927856</v>
       </c>
       <c r="L17" t="n">
-        <v>43.78979738429675</v>
+        <v>43.99928865228574</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93682831366512</v>
+        <v>99.92950783817182</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.47127262259454</v>
+        <v>79.94888306323354</v>
       </c>
       <c r="C18" t="n">
-        <v>35.91105073601889</v>
+        <v>36.20581825854519</v>
       </c>
       <c r="D18" t="n">
-        <v>1.285377531736704</v>
+        <v>1.29421459596856</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96098187259554</v>
+        <v>12.12047262666099</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578994593998635</v>
+        <v>0.7581449947866065</v>
       </c>
       <c r="G18" t="n">
-        <v>21.93061411740215</v>
+        <v>22.05963114704717</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21796683173824</v>
+        <v>37.21289956343683</v>
       </c>
       <c r="I18" t="n">
-        <v>1.581561188472888</v>
+        <v>1.765113917917106</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736871621249147</v>
+        <v>4.73840621741629</v>
       </c>
       <c r="K18" t="n">
-        <v>20.52872737740546</v>
+        <v>20.05111693676643</v>
       </c>
       <c r="L18" t="n">
-        <v>43.50753812901681</v>
+        <v>43.68427094251486</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94731624244116</v>
+        <v>99.94120613782648</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.53191678421709</v>
+        <v>79.08033086928641</v>
       </c>
       <c r="C19" t="n">
-        <v>35.2129296712755</v>
+        <v>35.60906588133799</v>
       </c>
       <c r="D19" t="n">
-        <v>1.251659112857954</v>
+        <v>1.263310353487978</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86736505152303</v>
+        <v>12.07635754848964</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583243810197925</v>
+        <v>0.7586153472093285</v>
       </c>
       <c r="G19" t="n">
-        <v>21.35532350058259</v>
+        <v>21.53287446224071</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23883334451967</v>
+        <v>37.23598641039425</v>
       </c>
       <c r="I19" t="n">
-        <v>1.320884012340345</v>
+        <v>1.471840827406197</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739527381373704</v>
+        <v>4.741345920058302</v>
       </c>
       <c r="K19" t="n">
-        <v>21.4680832157829</v>
+        <v>20.91966913071358</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27498231745921</v>
+        <v>43.42223404578404</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95599520451761</v>
+        <v>99.95096905783562</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.94708307118272</v>
+        <v>76.55962491629343</v>
       </c>
       <c r="C20" t="n">
-        <v>32.83129444577403</v>
+        <v>33.31487409557442</v>
       </c>
       <c r="D20" t="n">
-        <v>1.158371259558684</v>
+        <v>1.172620189115582</v>
       </c>
       <c r="E20" t="n">
-        <v>11.16641900581157</v>
+        <v>11.41395498864085</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586909164566793</v>
+        <v>0.7590206803900813</v>
       </c>
       <c r="G20" t="n">
-        <v>19.76368224186004</v>
+        <v>19.98707859426647</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2568327025658</v>
+        <v>37.25588184339032</v>
       </c>
       <c r="I20" t="n">
-        <v>1.101268717075703</v>
+        <v>1.227189368052126</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741818227854247</v>
+        <v>4.743879252438007</v>
       </c>
       <c r="K20" t="n">
-        <v>24.05291692881728</v>
+        <v>23.44037508370657</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07909740284366</v>
+        <v>43.20386635329105</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96330877743497</v>
+        <v>99.95911553257204</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.7084891085092</v>
+        <v>82.44300328839557</v>
       </c>
       <c r="C21" t="n">
-        <v>36.47534829640151</v>
+        <v>36.92076416554491</v>
       </c>
       <c r="D21" t="n">
-        <v>1.15907824520605</v>
+        <v>1.173483427789435</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11310611480668</v>
+        <v>13.36945163504947</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591539662641532</v>
+        <v>0.7595794427341449</v>
       </c>
       <c r="G21" t="n">
-        <v>21.46627187235627</v>
+        <v>21.64542933143899</v>
       </c>
       <c r="H21" t="n">
-        <v>38.97009888101751</v>
+        <v>38.92694522098483</v>
       </c>
       <c r="I21" t="n">
-        <v>1.496067739707589</v>
+        <v>1.820742713310275</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744712289150959</v>
+        <v>4.747371517088404</v>
       </c>
       <c r="K21" t="n">
-        <v>18.29151089149079</v>
+        <v>17.55699671160445</v>
       </c>
       <c r="L21" t="n">
-        <v>45.183302305254</v>
+        <v>45.46159234493989</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9501614931463</v>
+        <v>99.93935322208925</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_30_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43034227803824</v>
+        <v>43.69036838783879</v>
       </c>
       <c r="M2" t="n">
-        <v>99.21299653448472</v>
+        <v>95.86638673801053</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09953076970606</v>
+        <v>81.46310677353526</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95725561314313</v>
+        <v>43.21866232909082</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228894089334946</v>
+        <v>2.179708271336368</v>
       </c>
       <c r="E3" t="n">
-        <v>5.726632312658838</v>
+        <v>4.145085480931316</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429646964449821</v>
+        <v>0.7376232413338122</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9822819841404</v>
+        <v>32.78644524801786</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17637603646917</v>
+        <v>33.93066910135536</v>
       </c>
       <c r="I3" t="n">
-        <v>6.598852297876592</v>
+        <v>3.073430172224217</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643529352781138</v>
+        <v>4.610145258336326</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90046923029394</v>
+        <v>18.53689322646473</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90542757086736</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631524143044</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.28937965311414</v>
+        <v>88.59159688355672</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7871292295812</v>
+        <v>42.86172466910844</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190436256955797</v>
+        <v>2.185429041035115</v>
       </c>
       <c r="E4" t="n">
-        <v>6.546259643436955</v>
+        <v>6.557333968816472</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445281523023775</v>
+        <v>0.7395591759465332</v>
       </c>
       <c r="G4" t="n">
-        <v>33.39594416276952</v>
+        <v>33.49189554439907</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24829500590936</v>
+        <v>34.01972209354052</v>
       </c>
       <c r="I4" t="n">
-        <v>5.510615479850255</v>
+        <v>6.975412210153169</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653300951889859</v>
+        <v>4.622244849665832</v>
       </c>
       <c r="K4" t="n">
-        <v>12.71062034688588</v>
+        <v>11.4084031164433</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31894897081413</v>
+        <v>45.49796712235933</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81669854728121</v>
+        <v>99.76809490791106</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25281929759304</v>
+        <v>87.54818620197332</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60597112103388</v>
+        <v>42.89961430002401</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140344925308375</v>
+        <v>2.136165595397801</v>
       </c>
       <c r="E5" t="n">
-        <v>7.163282441017729</v>
+        <v>7.380476203583051</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458518135599805</v>
+        <v>0.7411995972406816</v>
       </c>
       <c r="G5" t="n">
-        <v>32.63223907460551</v>
+        <v>32.73692883330391</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30918342375911</v>
+        <v>34.09518147307135</v>
       </c>
       <c r="I5" t="n">
-        <v>4.600343784592454</v>
+        <v>5.825737016622275</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661573834749879</v>
+        <v>4.63249748275426</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74718070240696</v>
+        <v>12.45181379802665</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4937755243411</v>
+        <v>44.45481045166733</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84692734778194</v>
+        <v>99.80623854971799</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.94715041032558</v>
+        <v>86.26934652831568</v>
       </c>
       <c r="C6" t="n">
-        <v>42.01498600397309</v>
+        <v>42.5250606970653</v>
       </c>
       <c r="D6" t="n">
-        <v>2.076829713688088</v>
+        <v>2.075405850195345</v>
       </c>
       <c r="E6" t="n">
-        <v>7.590609688834685</v>
+        <v>7.981201377843465</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469755004917085</v>
+        <v>0.7425925694951098</v>
       </c>
       <c r="G6" t="n">
-        <v>31.66387012343341</v>
+        <v>31.8057803030084</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36087302261859</v>
+        <v>34.15925819677504</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83939548318593</v>
+        <v>4.863904671653879</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668596878073178</v>
+        <v>4.641203559344435</v>
       </c>
       <c r="K6" t="n">
-        <v>15.05284958967441</v>
+        <v>13.73065347168433</v>
       </c>
       <c r="L6" t="n">
-        <v>42.8043770790027</v>
+        <v>43.58245980301084</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87221267265021</v>
+        <v>99.83817397176047</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.40086409621135</v>
+        <v>84.72417994502123</v>
       </c>
       <c r="C7" t="n">
-        <v>41.06524808499835</v>
+        <v>41.73535583275535</v>
       </c>
       <c r="D7" t="n">
-        <v>2.001691079429898</v>
+        <v>2.001993889846558</v>
       </c>
       <c r="E7" t="n">
-        <v>7.84991746689296</v>
+        <v>8.375508927069477</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479319275875282</v>
+        <v>0.7437786629114033</v>
       </c>
       <c r="G7" t="n">
-        <v>30.51828753631871</v>
+        <v>30.68073544383211</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4048686690263</v>
+        <v>34.21381849392454</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203592869533897</v>
+        <v>4.059727884240872</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674574547422051</v>
+        <v>4.648616643196269</v>
       </c>
       <c r="K7" t="n">
-        <v>16.59913590378865</v>
+        <v>15.27582005497879</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22896613668004</v>
+        <v>42.85371564916437</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89335012546705</v>
+        <v>99.8648915368985</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.1386958538032</v>
+        <v>83.05531050126078</v>
       </c>
       <c r="C8" t="n">
-        <v>43.31535436374522</v>
+        <v>40.69699857493258</v>
       </c>
       <c r="D8" t="n">
-        <v>2.005907941769616</v>
+        <v>1.923231362544258</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644020636348621</v>
+        <v>8.610617022204888</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495075583182276</v>
+        <v>0.7447899182023983</v>
       </c>
       <c r="G8" t="n">
-        <v>31.00716851484066</v>
+        <v>29.47369266747544</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47734768263847</v>
+        <v>34.26033623731031</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57032128039867</v>
+        <v>3.387706304758483</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684422239488923</v>
+        <v>4.654936988764988</v>
       </c>
       <c r="K8" t="n">
-        <v>11.86130414619682</v>
+        <v>16.94468949873922</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63805444897378</v>
+        <v>42.24554170732154</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81471295891582</v>
+        <v>99.88722978099332</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.10673210262291</v>
+        <v>81.37201715931994</v>
       </c>
       <c r="C9" t="n">
-        <v>42.14829663348554</v>
+        <v>39.53955239303592</v>
       </c>
       <c r="D9" t="n">
-        <v>1.913795881649349</v>
+        <v>1.844445569687565</v>
       </c>
       <c r="E9" t="n">
-        <v>9.976211990682353</v>
+        <v>8.728939842624282</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750856824916473</v>
+        <v>0.7456522303235293</v>
       </c>
       <c r="G9" t="n">
-        <v>29.58330747370107</v>
+        <v>28.26629334441656</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53941394615777</v>
+        <v>34.30000259488234</v>
       </c>
       <c r="I9" t="n">
-        <v>4.650290829787944</v>
+        <v>2.826357137863612</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692855155727957</v>
+        <v>4.660326439522057</v>
       </c>
       <c r="K9" t="n">
-        <v>13.8932678973771</v>
+        <v>18.62798284068007</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80370432245962</v>
+        <v>41.73836181337403</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84526885332225</v>
+        <v>99.90589704709001</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.8488508305031</v>
+        <v>86.16778353073907</v>
       </c>
       <c r="C10" t="n">
-        <v>40.61216462518888</v>
+        <v>42.68554106864708</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812397539061182</v>
+        <v>1.846680287730732</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09451421178836</v>
+        <v>10.55249969653551</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520153547105383</v>
+        <v>0.7465556576300417</v>
       </c>
       <c r="G10" t="n">
-        <v>28.01589980244816</v>
+        <v>29.59152294575821</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59270631668477</v>
+        <v>35.63254259841251</v>
       </c>
       <c r="I10" t="n">
-        <v>3.881221638869222</v>
+        <v>3.132009484484311</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700095966940864</v>
+        <v>4.665972860187759</v>
       </c>
       <c r="K10" t="n">
-        <v>16.1511491694969</v>
+        <v>13.83221646926092</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10751146004234</v>
+        <v>43.37796848360465</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87082525472812</v>
+        <v>99.89572602151266</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.49718285390571</v>
+        <v>86.06064540377461</v>
       </c>
       <c r="C11" t="n">
-        <v>38.86221749236492</v>
+        <v>42.97883133622244</v>
       </c>
       <c r="D11" t="n">
-        <v>1.707896949645133</v>
+        <v>1.835276125162462</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05224968924703</v>
+        <v>10.97995198452204</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530115052133349</v>
+        <v>0.7473208825595354</v>
       </c>
       <c r="G11" t="n">
-        <v>26.40053784168687</v>
+        <v>29.46033595584626</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63852923981342</v>
+        <v>35.72062148636208</v>
       </c>
       <c r="I11" t="n">
-        <v>3.238635720716581</v>
+        <v>2.646383453325147</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706321907583344</v>
+        <v>4.670755515997095</v>
       </c>
       <c r="K11" t="n">
-        <v>18.50281714609429</v>
+        <v>13.93935459622538</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52715364934998</v>
+        <v>42.99369161192677</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89218828780919</v>
+        <v>99.9118775443746</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.00414530050422</v>
+        <v>84.35370030535475</v>
       </c>
       <c r="C12" t="n">
-        <v>36.87046894915709</v>
+        <v>41.68349310707672</v>
       </c>
       <c r="D12" t="n">
-        <v>1.598139843821999</v>
+        <v>1.762709974064101</v>
       </c>
       <c r="E12" t="n">
-        <v>9.856570411351411</v>
+        <v>10.91368251664521</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538699377043477</v>
+        <v>0.7479727088685187</v>
       </c>
       <c r="G12" t="n">
-        <v>24.70392106028227</v>
+        <v>28.29548497725514</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6780171344</v>
+        <v>35.75177763548278</v>
       </c>
       <c r="I12" t="n">
-        <v>2.701939802292023</v>
+        <v>2.207243062610774</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711687110652173</v>
+        <v>4.67482943042824</v>
       </c>
       <c r="K12" t="n">
-        <v>20.99585469949577</v>
+        <v>15.64629969464522</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04371424799391</v>
+        <v>42.59669654679679</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91003789664677</v>
+        <v>99.92648934851874</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.56431919858856</v>
+        <v>85.66254670970254</v>
       </c>
       <c r="C13" t="n">
-        <v>34.84794456822937</v>
+        <v>42.74335124574853</v>
       </c>
       <c r="D13" t="n">
-        <v>1.491766703060341</v>
+        <v>1.764141326103037</v>
       </c>
       <c r="E13" t="n">
-        <v>9.576148852791112</v>
+        <v>11.60860950887405</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546096606728954</v>
+        <v>0.7485800760915219</v>
       </c>
       <c r="G13" t="n">
-        <v>23.05961334686855</v>
+        <v>28.65672870069404</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71204439095319</v>
+        <v>36.11907600197487</v>
       </c>
       <c r="I13" t="n">
-        <v>2.253825865036894</v>
+        <v>2.086785620393018</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716310379205596</v>
+        <v>4.67862547557201</v>
       </c>
       <c r="K13" t="n">
-        <v>23.43568080141143</v>
+        <v>14.33745329029746</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64132074696219</v>
+        <v>42.84969238102119</v>
       </c>
       <c r="M13" t="n">
-        <v>99.924946116603</v>
+        <v>99.93049691706717</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.528001398698</v>
+        <v>83.90772177574658</v>
       </c>
       <c r="C14" t="n">
-        <v>39.12167736812759</v>
+        <v>41.31306601397239</v>
       </c>
       <c r="D14" t="n">
-        <v>1.493559942576776</v>
+        <v>1.691653124026433</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96099848793033</v>
+        <v>11.42164584584285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555167702498996</v>
+        <v>0.7490975778119856</v>
       </c>
       <c r="G14" t="n">
-        <v>24.95862998858541</v>
+        <v>27.47922964765673</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62506831662935</v>
+        <v>36.14404552035983</v>
       </c>
       <c r="I14" t="n">
-        <v>3.012248078664371</v>
+        <v>1.740190198723836</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721979814061872</v>
+        <v>4.681859861324909</v>
       </c>
       <c r="K14" t="n">
-        <v>16.471998601302</v>
+        <v>16.09227822425342</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30603631625306</v>
+        <v>42.53668949454106</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89971228568265</v>
+        <v>99.94203373276687</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.78675242956054</v>
+        <v>83.16991874105101</v>
       </c>
       <c r="C15" t="n">
-        <v>38.84582400890833</v>
+        <v>40.84056223579982</v>
       </c>
       <c r="D15" t="n">
-        <v>1.466221045015856</v>
+        <v>1.661635106784005</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16084921995061</v>
+        <v>11.4616048235203</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562811526279429</v>
+        <v>0.7495346498845449</v>
       </c>
       <c r="G15" t="n">
-        <v>24.501774251452</v>
+        <v>26.99161668631352</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66212316162849</v>
+        <v>36.16513429885035</v>
       </c>
       <c r="I15" t="n">
-        <v>2.512746394960979</v>
+        <v>1.45580161391989</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726757203924643</v>
+        <v>4.684591561778404</v>
       </c>
       <c r="K15" t="n">
-        <v>17.21324757043947</v>
+        <v>16.83008125894899</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85725486291153</v>
+        <v>42.28085808191035</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91632644225933</v>
+        <v>99.95150157665915</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.42107425654514</v>
+        <v>80.96839860166276</v>
       </c>
       <c r="C16" t="n">
-        <v>36.86844005088673</v>
+        <v>38.8650657957141</v>
       </c>
       <c r="D16" t="n">
-        <v>1.376444994278731</v>
+        <v>1.571228611799361</v>
       </c>
       <c r="E16" t="n">
-        <v>11.76554164139548</v>
+        <v>11.04029579274417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569381091957031</v>
+        <v>0.7499091852386041</v>
       </c>
       <c r="G16" t="n">
-        <v>23.0015417075083</v>
+        <v>25.5230527106152</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69397034242279</v>
+        <v>36.1832056733776</v>
       </c>
       <c r="I16" t="n">
-        <v>2.095774279271001</v>
+        <v>1.213774220146542</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730863182473144</v>
+        <v>4.686932407741274</v>
       </c>
       <c r="K16" t="n">
-        <v>19.57892574345484</v>
+        <v>19.03160139833724</v>
       </c>
       <c r="L16" t="n">
-        <v>43.48283569468728</v>
+        <v>42.06289387222866</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93020148902886</v>
+        <v>99.95956106628</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.24208862072145</v>
+        <v>85.33339615689972</v>
       </c>
       <c r="C17" t="n">
-        <v>38.17230780660751</v>
+        <v>41.65925550587417</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377625798686406</v>
+        <v>1.572144370978337</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58848268931065</v>
+        <v>12.55926077968172</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575874601391772</v>
+        <v>0.7503462548124544</v>
       </c>
       <c r="G17" t="n">
-        <v>23.48135855702916</v>
+        <v>26.80178436447802</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18553345143901</v>
+        <v>37.46815038424029</v>
       </c>
       <c r="I17" t="n">
-        <v>2.116579038247193</v>
+        <v>1.492045910131052</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734921625869857</v>
+        <v>4.689664092577839</v>
       </c>
       <c r="K17" t="n">
-        <v>17.75791137927856</v>
+        <v>14.66660384310029</v>
       </c>
       <c r="L17" t="n">
-        <v>43.99928865228574</v>
+        <v>43.62443475744068</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92950783817182</v>
+        <v>99.95029410641514</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.94888306323354</v>
+        <v>86.92362127076169</v>
       </c>
       <c r="C18" t="n">
-        <v>36.20581825854519</v>
+        <v>42.41302878542345</v>
       </c>
       <c r="D18" t="n">
-        <v>1.29421459596856</v>
+        <v>1.573518265006736</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12047262666099</v>
+        <v>13.18359395661574</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581449947866065</v>
+        <v>0.7510019810025862</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05963114704717</v>
+        <v>26.94197924940935</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21289956343683</v>
+        <v>37.50089373085549</v>
       </c>
       <c r="I18" t="n">
-        <v>1.765113917917106</v>
+        <v>2.278871706605595</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73840621741629</v>
+        <v>4.693762381266162</v>
       </c>
       <c r="K18" t="n">
-        <v>20.05111693676643</v>
+        <v>13.07637872923835</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68427094251486</v>
+        <v>44.43469642054723</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94120613782648</v>
+        <v>99.92410393520902</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.08033086928641</v>
+        <v>84.46820154010108</v>
       </c>
       <c r="C19" t="n">
-        <v>35.60906588133799</v>
+        <v>40.31118368062462</v>
       </c>
       <c r="D19" t="n">
-        <v>1.263310353487978</v>
+        <v>1.481973439562591</v>
       </c>
       <c r="E19" t="n">
-        <v>12.07635754848964</v>
+        <v>12.73334046697974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586153472093285</v>
+        <v>0.7515652175153397</v>
       </c>
       <c r="G19" t="n">
-        <v>21.53287446224071</v>
+        <v>25.37453714062875</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23598641039425</v>
+        <v>37.52901865348473</v>
       </c>
       <c r="I19" t="n">
-        <v>1.471840827406197</v>
+        <v>1.900484012459049</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741345920058302</v>
+        <v>4.697282609470872</v>
       </c>
       <c r="K19" t="n">
-        <v>20.91966913071358</v>
+        <v>15.53179845989892</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42223404578404</v>
+        <v>44.09371586762631</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95096905783562</v>
+        <v>99.93669800814986</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.55962491629343</v>
+        <v>81.79778887968749</v>
       </c>
       <c r="C20" t="n">
-        <v>33.31487409557442</v>
+        <v>37.93495971711438</v>
       </c>
       <c r="D20" t="n">
-        <v>1.172620189115582</v>
+        <v>1.38290394906372</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41395498864085</v>
+        <v>12.14624696188294</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590206803900813</v>
+        <v>0.7520505811193473</v>
       </c>
       <c r="G20" t="n">
-        <v>19.98707859426647</v>
+        <v>23.67825676268301</v>
       </c>
       <c r="H20" t="n">
-        <v>37.25588184339032</v>
+        <v>37.55325503287538</v>
       </c>
       <c r="I20" t="n">
-        <v>1.227189368052126</v>
+        <v>1.584759460067177</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743879252438007</v>
+        <v>4.70031613199592</v>
       </c>
       <c r="K20" t="n">
-        <v>23.44037508370657</v>
+        <v>18.2022111203125</v>
       </c>
       <c r="L20" t="n">
-        <v>43.20386635329105</v>
+        <v>43.8100379400048</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95911553257204</v>
+        <v>99.94720877743168</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.44300328839557</v>
+        <v>79.12650246381712</v>
       </c>
       <c r="C21" t="n">
-        <v>36.92076416554491</v>
+        <v>35.50827731944354</v>
       </c>
       <c r="D21" t="n">
-        <v>1.173483427789435</v>
+        <v>1.284333605609057</v>
       </c>
       <c r="E21" t="n">
-        <v>13.36945163504947</v>
+        <v>11.50071726915384</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595794427341449</v>
+        <v>0.7524692084858728</v>
       </c>
       <c r="G21" t="n">
-        <v>21.64542933143899</v>
+        <v>21.9905228437181</v>
       </c>
       <c r="H21" t="n">
-        <v>38.92694522098483</v>
+        <v>37.57415897292085</v>
       </c>
       <c r="I21" t="n">
-        <v>1.820742713310275</v>
+        <v>1.321368010892703</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747371517088404</v>
+        <v>4.702932553036704</v>
       </c>
       <c r="K21" t="n">
-        <v>17.55699671160445</v>
+        <v>20.87349753618286</v>
       </c>
       <c r="L21" t="n">
-        <v>45.46159234493989</v>
+        <v>43.57420404826062</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93935322208925</v>
+        <v>99.95597890388703</v>
       </c>
     </row>
   </sheetData>
